--- a/templates/manager_import_template.xlsx
+++ b/templates/manager_import_template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Менеджер" sheetId="1" r:id="Rc208460ad3a64a89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как использовать" sheetId="2" r:id="Reddd21814e804048"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Менеджер" sheetId="1" r:id="Refb4fe536561434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как использовать" sheetId="2" r:id="R743229a814ac4b9f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,10 +345,10 @@
         <x:v>https://supplier-brand.ru/catalog/ab-4451</x:v>
       </x:c>
       <x:c r="G2" s="13" t="str">
-        <x:v>https://cdn.supplier-brand.ru/ab-4451-1.jpg; https://cdn.supplier-brand.ru/ab-4451-2.jpg</x:v>
+        <x:v>https://cdn.supplier-brand.ru/ab-4451-1.jpg;https://cdn.supplier-brand.ru/ab-4451-2.jpg</x:v>
       </x:c>
       <x:c r="H2" s="13" t="str">
-        <x:v>Если прямых ссылок нет, можно оставить пусто</x:v>
+        <x:v>Для Спортмастера прямые ссылки лучше давать через ; без пробелов</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/templates/manager_import_template.xlsx
+++ b/templates/manager_import_template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Менеджер" sheetId="1" r:id="Refb4fe536561434b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как использовать" sheetId="2" r:id="R743229a814ac4b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Менеджер" sheetId="1" r:id="Ra2fa8a91bbc04208"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как использовать" sheetId="2" r:id="Rab5f2e40ab75409a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/templates/manager_import_template.xlsx
+++ b/templates/manager_import_template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Менеджер" sheetId="1" r:id="Ra2fa8a91bbc04208"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как использовать" sheetId="2" r:id="Rab5f2e40ab75409a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Менеджер" sheetId="1" r:id="R6ee3f90dbcb74496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как использовать" sheetId="2" r:id="Rdb05af2d0d1243de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -83,7 +83,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -96,19 +96,19 @@
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -118,8 +118,18 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -130,8 +140,11 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -300,248 +313,248 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="12" t="str">
+      <x:c r="A1" s="14" t="str">
         <x:v>article</x:v>
       </x:c>
-      <x:c r="B1" s="12" t="str">
+      <x:c r="B1" s="14" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="14" t="str">
         <x:v>quantity</x:v>
       </x:c>
-      <x:c r="D1" s="12" t="str">
+      <x:c r="D1" s="14" t="str">
         <x:v>supplier_site</x:v>
       </x:c>
-      <x:c r="E1" s="12" t="str">
+      <x:c r="E1" s="14" t="str">
         <x:v>supplier_article</x:v>
       </x:c>
-      <x:c r="F1" s="12" t="str">
+      <x:c r="F1" s="14" t="str">
         <x:v>product_url</x:v>
       </x:c>
-      <x:c r="G1" s="12" t="str">
+      <x:c r="G1" s="14" t="str">
         <x:v>image_urls_raw</x:v>
       </x:c>
-      <x:c r="H1" s="12" t="str">
+      <x:c r="H1" s="14" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="13" t="str">
+      <x:c r="A2" s="12" t="str">
         <x:v>TSR-10025</x:v>
       </x:c>
-      <x:c r="B2" s="13" t="str">
+      <x:c r="B2" s="12" t="str">
         <x:v>Кроссовки беговые мужские</x:v>
       </x:c>
-      <x:c r="C2" s="13" t="n">
+      <x:c r="C2" s="12" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D2" s="13" t="str">
+      <x:c r="D2" s="12" t="str">
         <x:v>supplier-brand.ru</x:v>
       </x:c>
-      <x:c r="E2" s="13" t="str">
+      <x:c r="E2" s="12" t="str">
         <x:v>AB-4451</x:v>
       </x:c>
-      <x:c r="F2" s="13" t="str">
+      <x:c r="F2" s="12" t="str">
         <x:v>https://supplier-brand.ru/catalog/ab-4451</x:v>
       </x:c>
-      <x:c r="G2" s="13" t="str">
+      <x:c r="G2" s="12" t="str">
         <x:v>https://cdn.supplier-brand.ru/ab-4451-1.jpg;https://cdn.supplier-brand.ru/ab-4451-2.jpg</x:v>
       </x:c>
-      <x:c r="H2" s="13" t="str">
-        <x:v>Для Спортмастера прямые ссылки лучше давать через ; без пробелов</x:v>
+      <x:c r="H2" s="12" t="str">
+        <x:v>Если прямые фото уже есть, парсер можно не ждать</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="13" t="str">
+      <x:c r="A3" s="12" t="str">
         <x:v>TSR-10026</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="12" t="str">
         <x:v>Рюкзак городской 20 л</x:v>
       </x:c>
-      <x:c r="C3" s="13" t="n">
+      <x:c r="C3" s="12" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D3" s="13" t="str">
+      <x:c r="D3" s="12" t="str">
         <x:v>supplier-brand.ru</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="str">
+      <x:c r="E3" s="12" t="str">
         <x:v>BP-220</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="str"/>
-      <x:c r="G3" s="13" t="str"/>
-      <x:c r="H3" s="13" t="str">
+      <x:c r="F3" s="12" t="str"/>
+      <x:c r="G3" s="12" t="str"/>
+      <x:c r="H3" s="12" t="str">
         <x:v>Тогда сервис попробует поиск по сайту и интернету</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str"/>
-      <x:c r="B4" s="14" t="str"/>
-      <x:c r="C4" s="14" t="str"/>
-      <x:c r="D4" s="14" t="str"/>
-      <x:c r="E4" s="14" t="str"/>
-      <x:c r="F4" s="14" t="str"/>
-      <x:c r="G4" s="14" t="str"/>
-      <x:c r="H4" s="14" t="str"/>
+      <x:c r="A4" s="15" t="str"/>
+      <x:c r="B4" s="15" t="str"/>
+      <x:c r="C4" s="15" t="str"/>
+      <x:c r="D4" s="15" t="str"/>
+      <x:c r="E4" s="15" t="str"/>
+      <x:c r="F4" s="15" t="str"/>
+      <x:c r="G4" s="15" t="str"/>
+      <x:c r="H4" s="15" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14"/>
-      <x:c r="B5" s="14"/>
-      <x:c r="C5" s="14"/>
-      <x:c r="D5" s="14"/>
-      <x:c r="E5" s="14"/>
-      <x:c r="F5" s="14"/>
-      <x:c r="G5" s="14"/>
-      <x:c r="H5" s="14"/>
+      <x:c r="A5" s="15"/>
+      <x:c r="B5" s="15"/>
+      <x:c r="C5" s="15"/>
+      <x:c r="D5" s="15"/>
+      <x:c r="E5" s="15"/>
+      <x:c r="F5" s="15"/>
+      <x:c r="G5" s="15"/>
+      <x:c r="H5" s="15"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="14"/>
-      <x:c r="B6" s="14"/>
-      <x:c r="C6" s="14"/>
-      <x:c r="D6" s="14"/>
-      <x:c r="E6" s="14"/>
-      <x:c r="F6" s="14"/>
-      <x:c r="G6" s="14"/>
-      <x:c r="H6" s="14"/>
+      <x:c r="A6" s="15"/>
+      <x:c r="B6" s="15"/>
+      <x:c r="C6" s="15"/>
+      <x:c r="D6" s="15"/>
+      <x:c r="E6" s="15"/>
+      <x:c r="F6" s="15"/>
+      <x:c r="G6" s="15"/>
+      <x:c r="H6" s="15"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="14"/>
-      <x:c r="B7" s="14"/>
-      <x:c r="C7" s="14"/>
-      <x:c r="D7" s="14"/>
-      <x:c r="E7" s="14"/>
-      <x:c r="F7" s="14"/>
-      <x:c r="G7" s="14"/>
-      <x:c r="H7" s="14"/>
+      <x:c r="A7" s="15"/>
+      <x:c r="B7" s="15"/>
+      <x:c r="C7" s="15"/>
+      <x:c r="D7" s="15"/>
+      <x:c r="E7" s="15"/>
+      <x:c r="F7" s="15"/>
+      <x:c r="G7" s="15"/>
+      <x:c r="H7" s="15"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="14"/>
-      <x:c r="B8" s="14"/>
-      <x:c r="C8" s="14"/>
-      <x:c r="D8" s="14"/>
-      <x:c r="E8" s="14"/>
-      <x:c r="F8" s="14"/>
-      <x:c r="G8" s="14"/>
-      <x:c r="H8" s="14"/>
+      <x:c r="A8" s="15"/>
+      <x:c r="B8" s="15"/>
+      <x:c r="C8" s="15"/>
+      <x:c r="D8" s="15"/>
+      <x:c r="E8" s="15"/>
+      <x:c r="F8" s="15"/>
+      <x:c r="G8" s="15"/>
+      <x:c r="H8" s="15"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="14"/>
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="14"/>
-      <x:c r="D9" s="14"/>
-      <x:c r="E9" s="14"/>
-      <x:c r="F9" s="14"/>
-      <x:c r="G9" s="14"/>
-      <x:c r="H9" s="14"/>
+      <x:c r="A9" s="15"/>
+      <x:c r="B9" s="15"/>
+      <x:c r="C9" s="15"/>
+      <x:c r="D9" s="15"/>
+      <x:c r="E9" s="15"/>
+      <x:c r="F9" s="15"/>
+      <x:c r="G9" s="15"/>
+      <x:c r="H9" s="15"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="14"/>
-      <x:c r="B10" s="14"/>
-      <x:c r="C10" s="14"/>
-      <x:c r="D10" s="14"/>
-      <x:c r="E10" s="14"/>
-      <x:c r="F10" s="14"/>
-      <x:c r="G10" s="14"/>
-      <x:c r="H10" s="14"/>
+      <x:c r="A10" s="15"/>
+      <x:c r="B10" s="15"/>
+      <x:c r="C10" s="15"/>
+      <x:c r="D10" s="15"/>
+      <x:c r="E10" s="15"/>
+      <x:c r="F10" s="15"/>
+      <x:c r="G10" s="15"/>
+      <x:c r="H10" s="15"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="14"/>
-      <x:c r="B11" s="14"/>
-      <x:c r="C11" s="14"/>
-      <x:c r="D11" s="14"/>
-      <x:c r="E11" s="14"/>
-      <x:c r="F11" s="14"/>
-      <x:c r="G11" s="14"/>
-      <x:c r="H11" s="14"/>
+      <x:c r="A11" s="15"/>
+      <x:c r="B11" s="15"/>
+      <x:c r="C11" s="15"/>
+      <x:c r="D11" s="15"/>
+      <x:c r="E11" s="15"/>
+      <x:c r="F11" s="15"/>
+      <x:c r="G11" s="15"/>
+      <x:c r="H11" s="15"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="14"/>
-      <x:c r="B12" s="14"/>
-      <x:c r="C12" s="14"/>
-      <x:c r="D12" s="14"/>
-      <x:c r="E12" s="14"/>
-      <x:c r="F12" s="14"/>
-      <x:c r="G12" s="14"/>
-      <x:c r="H12" s="14"/>
+      <x:c r="A12" s="15"/>
+      <x:c r="B12" s="15"/>
+      <x:c r="C12" s="15"/>
+      <x:c r="D12" s="15"/>
+      <x:c r="E12" s="15"/>
+      <x:c r="F12" s="15"/>
+      <x:c r="G12" s="15"/>
+      <x:c r="H12" s="15"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="14"/>
-      <x:c r="B13" s="14"/>
-      <x:c r="C13" s="14"/>
-      <x:c r="D13" s="14"/>
-      <x:c r="E13" s="14"/>
-      <x:c r="F13" s="14"/>
-      <x:c r="G13" s="14"/>
-      <x:c r="H13" s="14"/>
+      <x:c r="A13" s="15"/>
+      <x:c r="B13" s="15"/>
+      <x:c r="C13" s="15"/>
+      <x:c r="D13" s="15"/>
+      <x:c r="E13" s="15"/>
+      <x:c r="F13" s="15"/>
+      <x:c r="G13" s="15"/>
+      <x:c r="H13" s="15"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="14"/>
-      <x:c r="B14" s="14"/>
-      <x:c r="C14" s="14"/>
-      <x:c r="D14" s="14"/>
-      <x:c r="E14" s="14"/>
-      <x:c r="F14" s="14"/>
-      <x:c r="G14" s="14"/>
-      <x:c r="H14" s="14"/>
+      <x:c r="A14" s="15"/>
+      <x:c r="B14" s="15"/>
+      <x:c r="C14" s="15"/>
+      <x:c r="D14" s="15"/>
+      <x:c r="E14" s="15"/>
+      <x:c r="F14" s="15"/>
+      <x:c r="G14" s="15"/>
+      <x:c r="H14" s="15"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="14"/>
-      <x:c r="B15" s="14"/>
-      <x:c r="C15" s="14"/>
-      <x:c r="D15" s="14"/>
-      <x:c r="E15" s="14"/>
-      <x:c r="F15" s="14"/>
-      <x:c r="G15" s="14"/>
-      <x:c r="H15" s="14"/>
+      <x:c r="A15" s="15"/>
+      <x:c r="B15" s="15"/>
+      <x:c r="C15" s="15"/>
+      <x:c r="D15" s="15"/>
+      <x:c r="E15" s="15"/>
+      <x:c r="F15" s="15"/>
+      <x:c r="G15" s="15"/>
+      <x:c r="H15" s="15"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="14"/>
-      <x:c r="B16" s="14"/>
-      <x:c r="C16" s="14"/>
-      <x:c r="D16" s="14"/>
-      <x:c r="E16" s="14"/>
-      <x:c r="F16" s="14"/>
-      <x:c r="G16" s="14"/>
-      <x:c r="H16" s="14"/>
+      <x:c r="A16" s="15"/>
+      <x:c r="B16" s="15"/>
+      <x:c r="C16" s="15"/>
+      <x:c r="D16" s="15"/>
+      <x:c r="E16" s="15"/>
+      <x:c r="F16" s="15"/>
+      <x:c r="G16" s="15"/>
+      <x:c r="H16" s="15"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="14"/>
-      <x:c r="B17" s="14"/>
-      <x:c r="C17" s="14"/>
-      <x:c r="D17" s="14"/>
-      <x:c r="E17" s="14"/>
-      <x:c r="F17" s="14"/>
-      <x:c r="G17" s="14"/>
-      <x:c r="H17" s="14"/>
+      <x:c r="A17" s="15"/>
+      <x:c r="B17" s="15"/>
+      <x:c r="C17" s="15"/>
+      <x:c r="D17" s="15"/>
+      <x:c r="E17" s="15"/>
+      <x:c r="F17" s="15"/>
+      <x:c r="G17" s="15"/>
+      <x:c r="H17" s="15"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="14"/>
-      <x:c r="B18" s="14"/>
-      <x:c r="C18" s="14"/>
-      <x:c r="D18" s="14"/>
-      <x:c r="E18" s="14"/>
-      <x:c r="F18" s="14"/>
-      <x:c r="G18" s="14"/>
-      <x:c r="H18" s="14"/>
+      <x:c r="A18" s="15"/>
+      <x:c r="B18" s="15"/>
+      <x:c r="C18" s="15"/>
+      <x:c r="D18" s="15"/>
+      <x:c r="E18" s="15"/>
+      <x:c r="F18" s="15"/>
+      <x:c r="G18" s="15"/>
+      <x:c r="H18" s="15"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="14"/>
-      <x:c r="B19" s="14"/>
-      <x:c r="C19" s="14"/>
-      <x:c r="D19" s="14"/>
-      <x:c r="E19" s="14"/>
-      <x:c r="F19" s="14"/>
-      <x:c r="G19" s="14"/>
-      <x:c r="H19" s="14"/>
+      <x:c r="A19" s="15"/>
+      <x:c r="B19" s="15"/>
+      <x:c r="C19" s="15"/>
+      <x:c r="D19" s="15"/>
+      <x:c r="E19" s="15"/>
+      <x:c r="F19" s="15"/>
+      <x:c r="G19" s="15"/>
+      <x:c r="H19" s="15"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="14"/>
-      <x:c r="B20" s="14"/>
-      <x:c r="C20" s="14"/>
-      <x:c r="D20" s="14"/>
-      <x:c r="E20" s="14"/>
-      <x:c r="F20" s="14"/>
-      <x:c r="G20" s="14"/>
-      <x:c r="H20" s="14"/>
+      <x:c r="A20" s="15"/>
+      <x:c r="B20" s="15"/>
+      <x:c r="C20" s="15"/>
+      <x:c r="D20" s="15"/>
+      <x:c r="E20" s="15"/>
+      <x:c r="F20" s="15"/>
+      <x:c r="G20" s="15"/>
+      <x:c r="H20" s="15"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -552,109 +565,98 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.710000038146973" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="50.709999084472656" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12.140000343322754" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="53.56999969482422" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="45" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="12" t="str">
+      <x:c r="A1" s="14" t="str">
         <x:v>UpdatPic templates</x:v>
       </x:c>
-      <x:c r="B1" s="12"/>
-      <x:c r="C1" s="12"/>
+      <x:c r="B1" s="14"/>
+      <x:c r="C1" s="14"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="14"/>
-      <x:c r="B2" s="14"/>
-      <x:c r="C2" s="14"/>
+      <x:c r="A2" s="15"/>
+      <x:c r="B2" s="15"/>
+      <x:c r="C2" s="15"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="30" t="str">
+      <x:c r="A3" s="24" t="str">
         <x:v>Шаг</x:v>
       </x:c>
-      <x:c r="B3" s="30" t="str">
+      <x:c r="B3" s="24" t="str">
         <x:v>Что делать</x:v>
       </x:c>
-      <x:c r="C3" s="30" t="str">
+      <x:c r="C3" s="24" t="str">
         <x:v>Результат</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="28" t="str">
+      <x:c r="A4" s="32" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B4" s="28" t="str">
-        <x:v>На листе Менеджер заполнить строки под заголовками из первой строки</x:v>
-      </x:c>
-      <x:c r="C4" s="28" t="str">
-        <x:v>Файл можно сразу загружать в раздел Каталог фото</x:v>
+      <x:c r="B4" s="32" t="str">
+        <x:v>На листе Менеджер заполнить article и name</x:v>
+      </x:c>
+      <x:c r="C4" s="32" t="str">
+        <x:v>Файл можно загружать в Каталог фото</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="28" t="str">
+      <x:c r="A5" s="32" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="str">
-        <x:v>Проверить, что у нужных товаров появились фото в локальном каталоге</x:v>
-      </x:c>
-      <x:c r="C5" s="28" t="str">
-        <x:v>Товары будут готовы к клиентской упаковке</x:v>
+      <x:c r="B5" s="32" t="str">
+        <x:v>Если прямые фото уже есть, вставить их в image_urls_raw</x:v>
+      </x:c>
+      <x:c r="C5" s="32" t="str">
+        <x:v>Сервис пойдёт по ним без лишнего поиска</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="28" t="str">
+      <x:c r="A6" s="32" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="28" t="str">
-        <x:v>На листе Клиент заполнить article и client_code и загрузить файл в раздел Клиенты</x:v>
-      </x:c>
-      <x:c r="C6" s="28" t="str">
-        <x:v>Сервис соберёт ZIP-архив под правила клиента</x:v>
+      <x:c r="B6" s="32" t="str">
+        <x:v>Если прямых фото нет, заполнить сайт поставщика или product_url</x:v>
+      </x:c>
+      <x:c r="C6" s="32" t="str">
+        <x:v>Сервис попробует сам найти картинки</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="28" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B7" s="28" t="str">
-        <x:v>Скачать архив и при необходимости проверить несколько файлов глазами</x:v>
-      </x:c>
-      <x:c r="C7" s="28" t="str">
-        <x:v>Можно передавать архив менеджеру или клиенту</x:v>
+      <x:c r="B7" s="32" t="str">
+        <x:v>Проверить локальный каталог и затем перейти в раздел Клиенты</x:v>
+      </x:c>
+      <x:c r="C7" s="32" t="str">
+        <x:v>Дальше фото можно упаковать под площадку</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="28" t="str">
-        <x:v>Поля менеджера</x:v>
-      </x:c>
-      <x:c r="B8" s="28" t="str">
+      <x:c r="A8" s="32" t="str">
+        <x:v>Поля</x:v>
+      </x:c>
+      <x:c r="B8" s="32" t="str">
         <x:v>article и name обязательны; quantity, supplier_site, supplier_article, product_url, image_urls_raw, notes опциональны</x:v>
       </x:c>
-      <x:c r="C8" s="28" t="str">
-        <x:v>Прямые ссылки на фото указывайте через ;</x:v>
+      <x:c r="C8" s="32" t="str">
+        <x:v>Ссылки на фото можно разделять ; , пробелом или переносом строки</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="28" t="str">
-        <x:v>Поля клиента</x:v>
-      </x:c>
-      <x:c r="B9" s="28" t="str">
-        <x:v>client_code это код цветомодели, штрихкод или другой код клиента</x:v>
-      </x:c>
-      <x:c r="C9" s="28" t="str">
-        <x:v>Для разных клиентов можно использовать отдельные файлы сопоставления</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="28" t="str">
+      <x:c r="A9" s="32" t="str">
         <x:v>Важно</x:v>
       </x:c>
-      <x:c r="B10" s="28" t="str">
-        <x:v>Автопоиск не гарантирует прохождение модерации маркетплейса</x:v>
-      </x:c>
-      <x:c r="C10" s="28" t="str">
-        <x:v>Нужна ручная проверка качества и контента фото</x:v>
+      <x:c r="B9" s="32" t="str">
+        <x:v>Поиск из интернета не гарантирует модерацию маркетплейса</x:v>
+      </x:c>
+      <x:c r="C9" s="32" t="str">
+        <x:v>Нужна ручная проверка финального набора</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
